--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -435,13 +435,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
       <c r="E5">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6">
@@ -480,10 +480,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>0.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E15">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>0.01</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="23">
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -942,7 +942,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>0.27</v>
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="31">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="3">
@@ -438,10 +438,10 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -480,10 +480,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -501,10 +501,10 @@
         <v>49</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>0.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="17">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -753,10 +753,10 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20">
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
         <v>5</v>
       </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
       <c r="E22">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="23">
@@ -834,24 +834,24 @@
         </is>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mortalidad por dengue</t>
+          <t>Vigilancia integrada de muertes en menores de cinco anos por infeccion respiratoria aguda - enfermedad diarreica aguda y/o desnutricion</t>
         </is>
       </c>
       <c r="C24">
@@ -867,43 +867,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vigilancia integrada de muertes en menores de cinco anos por infeccion respiratoria aguda - enfermedad diarreica aguda y/o desnutricion</t>
+          <t>Parotiditis</t>
         </is>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Parotiditis</t>
+          <t>Sarampion</t>
         </is>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="28">
@@ -942,7 +942,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0.27</v>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>0.09</v>
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="32">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="3">
@@ -435,13 +435,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="5">
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="6">
@@ -480,10 +480,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="7">
@@ -498,115 +498,115 @@
         </is>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hepatitis a</t>
+          <t>Fiebre tifoidea y paratifoidea</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hepatitis b, c y coinfeccion hepatitis b y delta</t>
+          <t>Hepatitis a</t>
         </is>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Enfermedades huerfanas - raras</t>
+          <t>Hepatitis b, c y coinfeccion hepatitis b y delta</t>
         </is>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ira por virus nuevo</t>
+          <t>Enfermedades huerfanas - raras</t>
         </is>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Infeccion respiratoria aguda grave irag inusitada</t>
+          <t>Ira por virus nuevo</t>
         </is>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -615,264 +615,264 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infecciones de sitio quirurgico asociadas a procedimiento medico quirurgico</t>
+          <t>Infeccion respiratoria aguda grave irag inusitada</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Enfermedad transmitida por alimentos o agua (eta)</t>
+          <t>Infecciones de sitio quirurgico asociadas a procedimiento medico quirurgico</t>
         </is>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intento de suicidio</t>
+          <t>Enfermedad transmitida por alimentos o agua (eta)</t>
         </is>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.08</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iad - infecciones asociadas a dispositivos - individual</t>
+          <t>Intento de suicidio</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intoxicaciones</t>
+          <t>Iad - infecciones asociadas a dispositivos - individual</t>
         </is>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Leishmaniasis cutanea</t>
+          <t>Intoxicaciones</t>
         </is>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Leishmaniasis cutanea</t>
         </is>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Lepra</t>
         </is>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Meningitis bacteriana y enfermedad meningoc”cica</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Morbilidad materna extrema</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>0.16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mortalidad perinatal y neonatal tardia</t>
+          <t>Meningitis bacteriana y enfermedad meningoc”cica</t>
         </is>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0.27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vigilancia integrada de muertes en menores de cinco anos por infeccion respiratoria aguda - enfermedad diarreica aguda y/o desnutricion</t>
+          <t>Morbilidad materna extrema</t>
         </is>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Parotiditis</t>
+          <t>Mortalidad perinatal y neonatal tardia</t>
         </is>
       </c>
       <c r="C25">
@@ -888,40 +888,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sarampion</t>
+          <t>Vigilancia integrada de muertes en menores de cinco anos por infeccion respiratoria aguda - enfermedad diarreica aguda y/o desnutricion</t>
         </is>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sifilis congenita</t>
+          <t>Parotiditis</t>
         </is>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0.37</v>
@@ -930,33 +930,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sifilis gestacional</t>
+          <t>Sarampion</t>
         </is>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0.27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>740</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tos ferina</t>
+          <t>Sifilis congenita</t>
         </is>
       </c>
       <c r="C29">
@@ -972,64 +972,106 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>750</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Sifilis gestacional</t>
         </is>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>800</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Varicela individual</t>
+          <t>Tos ferina</t>
         </is>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>0.13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Varicela individual</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Vih/sida/mortalidad por sida</t>
         </is>
       </c>
-      <c r="C32">
+      <c r="C34">
         <v>8</v>
       </c>
-      <c r="D32">
-        <v>6</v>
-      </c>
-      <c r="E32">
-        <v>0.12</v>
+      <c r="D34">
+        <v>16</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>0.37</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="3">
@@ -414,13 +414,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="4">
@@ -435,13 +435,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="6">
@@ -480,10 +480,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="7">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="8">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="10">
@@ -564,10 +564,10 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="12">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E16">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="17">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="18">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="22">
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>0.16</v>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1026,10 +1026,10 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="33">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>0.04</v>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -396,10 +396,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3">
@@ -417,10 +417,10 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="4">
@@ -435,234 +435,234 @@
         </is>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Chagas</t>
         </is>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0.22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Defectos congenitos</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>0.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agresiones por animales potencialmente transmisores de rabia</t>
+          <t>Defectos congenitos</t>
         </is>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fiebre tifoidea y paratifoidea</t>
+          <t>Dengue grave</t>
         </is>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hepatitis a</t>
+          <t>Agresiones por animales potencialmente transmisores de rabia</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hepatitis b, c y coinfeccion hepatitis b y delta</t>
+          <t>Fiebre tifoidea y paratifoidea</t>
         </is>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Enfermedades huerfanas - raras</t>
+          <t>Hepatitis a</t>
         </is>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.04</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ira por virus nuevo</t>
+          <t>Hepatitis b, c y coinfeccion hepatitis b y delta</t>
         </is>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infeccion respiratoria aguda grave irag inusitada</t>
+          <t>Enfermedades huerfanas - raras</t>
         </is>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Infecciones de sitio quirurgico asociadas a procedimiento medico quirurgico</t>
+          <t>Ira por virus nuevo</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Enfermedad transmitida por alimentos o agua (eta)</t>
+          <t>Infeccion respiratoria aguda grave irag inusitada</t>
         </is>
       </c>
       <c r="C15">
@@ -678,138 +678,138 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intento de suicidio</t>
+          <t>Infecciones de sitio quirurgico asociadas a procedimiento medico quirurgico</t>
         </is>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iad - infecciones asociadas a dispositivos - individual</t>
+          <t>Enfermedad transmitida por alimentos o agua (eta)</t>
         </is>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intoxicaciones</t>
+          <t>Intento de suicidio</t>
         </is>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leishmaniasis cutanea</t>
+          <t>Iad - infecciones asociadas a dispositivos - individual</t>
         </is>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lepra</t>
+          <t>Intoxicaciones</t>
         </is>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Leishmaniasis cutanea</t>
         </is>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Lepra</t>
         </is>
       </c>
       <c r="C22">
@@ -825,117 +825,117 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Meningitis bacteriana y enfermedad meningoc”cica</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Morbilidad materna extrema</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mortalidad perinatal y neonatal tardia</t>
+          <t>Meningitis bacteriana y enfermedad meningoc”cica</t>
         </is>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vigilancia integrada de muertes en menores de cinco anos por infeccion respiratoria aguda - enfermedad diarreica aguda y/o desnutricion</t>
+          <t>Morbilidad materna extrema</t>
         </is>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parotiditis</t>
+          <t>Mortalidad perinatal y neonatal tardia</t>
         </is>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sarampion</t>
+          <t>Vigilancia integrada de muertes en menores de cinco anos por infeccion respiratoria aguda - enfermedad diarreica aguda y/o desnutricion</t>
         </is>
       </c>
       <c r="C28">
@@ -951,54 +951,54 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sifilis congenita</t>
+          <t>Parotiditis</t>
         </is>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sifilis gestacional</t>
+          <t>Sarampion</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>740</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tos ferina</t>
+          <t>Sifilis congenita</t>
         </is>
       </c>
       <c r="C31">
@@ -1014,64 +1014,106 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Sifilis gestacional</t>
         </is>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>800</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Varicela individual</t>
+          <t>Tos ferina</t>
         </is>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>0.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Varicela individual</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Vih/sida/mortalidad por sida</t>
         </is>
       </c>
-      <c r="C34">
-        <v>6</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>0.09</v>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -384,148 +384,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Desnutrici”n aguda en menores de 5 anos</t>
+          <t>Accidente ofidico</t>
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cancer en menores de 18 anos</t>
+          <t>Desnutrici”n aguda en menores de 5 anos</t>
         </is>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cancer de la mama y cuello uterino</t>
+          <t>Cancer en menores de 18 anos</t>
         </is>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chagas</t>
+          <t>Cancer de la mama y cuello uterino</t>
         </is>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Chagas</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Defectos congenitos</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
       <c r="E7">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dengue grave</t>
+          <t>Defectos congenitos</t>
         </is>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E9">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
       <c r="E13">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="14">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="20">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="21">
@@ -837,10 +837,10 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="24">
@@ -900,10 +900,10 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="27">
@@ -921,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <v>0.37</v>
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="30">
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34">
         <v>7</v>
       </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
       <c r="E34">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="35">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E36">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/poisson.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/poisson.xlsx
@@ -417,10 +417,10 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="4">
@@ -456,13 +456,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="9">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -606,10 +606,10 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="13">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="17">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="18">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -837,10 +837,10 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="24">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="28">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="30">
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
